--- a/data/trans_orig/IP07C17-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C17-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de gustarle ir al colegio en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11930</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>22591</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34869</t>
+          <t>34992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21137</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33881</t>
+          <t>33824</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34018</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46611</t>
+          <t>45348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63712</t>
+          <t>63053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>17381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>29640</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26899</t>
+          <t>26688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>42619</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>8978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31145</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28659</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37405</t>
+          <t>37668</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56158</t>
+          <t>56883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38850</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54025</t>
+          <t>54286</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21777</t>
+          <t>21770</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36142</t>
+          <t>35539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>64608</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85533</t>
+          <t>85482</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>12971</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25036</t>
+          <t>25128</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23456</t>
+          <t>24317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38180</t>
+          <t>38320</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>41131</t>
+          <t>39733</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59711</t>
+          <t>59512</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6714</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12495</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17968</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23896</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>10145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20659</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26734</t>
+          <t>25900</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41594</t>
+          <t>41600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>31581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18561</t>
+          <t>19023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31084</t>
+          <t>30537</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41750</t>
+          <t>42664</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58933</t>
+          <t>59548</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13526</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24366</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34379</t>
+          <t>34570</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7393</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>485</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>16870</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30352</t>
+          <t>30550</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13246</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26261</t>
+          <t>25474</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33311</t>
+          <t>32158</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51512</t>
+          <t>51058</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25331</t>
+          <t>24546</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39958</t>
+          <t>39864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28410</t>
+          <t>27282</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43026</t>
+          <t>42553</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56392</t>
+          <t>56952</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77781</t>
+          <t>78505</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,37%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26937</t>
+          <t>27738</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>26096</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43337</t>
+          <t>43579</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13554</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18721</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,47 +3245,47 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>4995</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>8912</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>2,72%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>12,47%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>4995</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2276</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>9458</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16443</t>
+          <t>15416</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>71387</t>
+          <t>71501</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>95815</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53626</t>
+          <t>54046</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76799</t>
+          <t>76261</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>131401</t>
+          <t>132584</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>164837</t>
+          <t>166964</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>116210</t>
+          <t>116890</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>144178</t>
+          <t>144807</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>102097</t>
+          <t>102775</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>128459</t>
+          <t>128394</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>227655</t>
+          <t>227618</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>266108</t>
+          <t>266085</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>42738</t>
+          <t>42339</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63346</t>
+          <t>63512</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>79686</t>
+          <t>79948</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>105234</t>
+          <t>105658</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>130913</t>
+          <t>128052</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>164314</t>
+          <t>162636</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19955</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23309</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21556</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>38895</t>
+          <t>39480</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>17225</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>21122</t>
+          <t>21767</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>38634</t>
+          <t>39169</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de gustarle ir al colegio en 2012 (tasa de respuesta: 95,2%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio en 2012 (tasa de respuesta: 95,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21151</t>
+          <t>21140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33629</t>
+          <t>33818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22440</t>
+          <t>22041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36617</t>
+          <t>36204</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47038</t>
+          <t>47289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66561</t>
+          <t>65478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,58%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29069</t>
+          <t>28998</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29853</t>
+          <t>29236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36516</t>
+          <t>36196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54785</t>
+          <t>54412</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16350</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>21709</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33424</t>
+          <t>33519</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8909</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33139</t>
+          <t>33805</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48747</t>
+          <t>48707</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22373</t>
+          <t>22347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36590</t>
+          <t>36626</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59569</t>
+          <t>60256</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81425</t>
+          <t>81664</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27316</t>
+          <t>27863</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29619</t>
+          <t>29292</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44186</t>
+          <t>44175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61895</t>
+          <t>59914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82532</t>
+          <t>82557</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8676</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>19475</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>24149</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24022</t>
+          <t>22686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39344</t>
+          <t>39887</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16774</t>
+          <t>17530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>721</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7175</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19964</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32177</t>
+          <t>32403</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>34391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44221</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63114</t>
+          <t>62806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,01%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14010</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25826</t>
+          <t>25998</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22981</t>
+          <t>23365</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28716</t>
+          <t>28974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>44994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>20056</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18735</t>
+          <t>18340</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34813</t>
+          <t>35037</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11574</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>17550</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31620</t>
+          <t>31947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30237</t>
+          <t>28938</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37265</t>
+          <t>36612</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57430</t>
+          <t>57364</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29272</t>
+          <t>29391</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45322</t>
+          <t>44653</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45831</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63123</t>
+          <t>63559</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85334</t>
+          <t>85860</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>13028</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27262</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>28433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30682</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48828</t>
+          <t>49203</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>11870</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>104600</t>
+          <t>105430</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132757</t>
+          <t>132903</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>94179</t>
+          <t>91624</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>122069</t>
+          <t>121567</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>206927</t>
+          <t>205937</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>246981</t>
+          <t>247934</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>100780</t>
+          <t>99071</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>127580</t>
+          <t>128486</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>100838</t>
+          <t>101430</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>130016</t>
+          <t>129835</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>207403</t>
+          <t>208681</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>247616</t>
+          <t>249088</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>46179</t>
+          <t>46144</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67586</t>
+          <t>69547</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>54481</t>
+          <t>55101</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>79442</t>
+          <t>79226</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>105338</t>
+          <t>106391</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>138847</t>
+          <t>137411</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19885</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28119</t>
+          <t>29228</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>25019</t>
+          <t>24852</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>44637</t>
+          <t>43091</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14163</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>23063</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>35025</t>
+          <t>32647</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de gustarle ir al colegio en 2016 (tasa de respuesta: 95,57%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio en 2016 (tasa de respuesta: 95,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>13397</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26292</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16369</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30709</t>
+          <t>29527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34024</t>
+          <t>33648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52114</t>
+          <t>52954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26944</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41343</t>
+          <t>41232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23126</t>
+          <t>23412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37424</t>
+          <t>37241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>54535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74368</t>
+          <t>74224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,0%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>18989</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>15225</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29782</t>
+          <t>30116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13535</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29181</t>
+          <t>28552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44603</t>
+          <t>44855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29675</t>
+          <t>29025</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45402</t>
+          <t>45008</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>63465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85240</t>
+          <t>84883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,29%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28240</t>
+          <t>28095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43408</t>
+          <t>43258</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34026</t>
+          <t>33539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50625</t>
+          <t>50002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66391</t>
+          <t>65467</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89144</t>
+          <t>87777</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29212</t>
+          <t>29019</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13935</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>27396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32767</t>
+          <t>33671</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51348</t>
+          <t>52804</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>14251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25474</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38282</t>
+          <t>38293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30649</t>
+          <t>30509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46284</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65619</t>
+          <t>65222</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,13%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23586</t>
+          <t>23349</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>17936</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31324</t>
+          <t>31966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33622</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50819</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>19616</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25971</t>
+          <t>26282</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>24310</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41498</t>
+          <t>40916</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14901</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10662</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>26895</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44650</t>
+          <t>44106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>14541</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>28193</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46228</t>
+          <t>46137</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67537</t>
+          <t>67659</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36777</t>
+          <t>36541</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53969</t>
+          <t>54781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37733</t>
+          <t>38258</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54438</t>
+          <t>55486</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>79399</t>
+          <t>79930</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103187</t>
+          <t>103412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,84%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>9816</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21642</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28083</t>
+          <t>27914</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>26720</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45309</t>
+          <t>44640</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11604</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>17146</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16234</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>109354</t>
+          <t>108933</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>138006</t>
+          <t>138204</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>90126</t>
+          <t>91587</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>118410</t>
+          <t>120178</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>207309</t>
+          <t>209057</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>247274</t>
+          <t>249318</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>117067</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>146554</t>
+          <t>147006</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>127357</t>
+          <t>127977</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>157520</t>
+          <t>158094</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>254266</t>
+          <t>251008</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>297069</t>
+          <t>295886</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48050</t>
+          <t>48006</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>70161</t>
+          <t>71175</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>59817</t>
+          <t>60416</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>85350</t>
+          <t>85433</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>114154</t>
+          <t>114904</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>147919</t>
+          <t>148096</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26772</t>
+          <t>26269</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>27821</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>48002</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>19186</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>17464</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16350</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32282</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
